--- a/assets/xlsx/주별투자수익_2026-08-03_2026-08-27.xlsx
+++ b/assets/xlsx/주별투자수익_2026-08-03_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>202824401</v>
+        <v>182300943</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>202702969</v>
+        <v>182219113</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>121432</v>
+        <v>81830</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0818</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>200513829</v>
+        <v>180356267</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>200405709</v>
+        <v>180292609</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>108120</v>
+        <v>63658</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0711</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>204072049</v>
+        <v>182978146</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>203958761</v>
+        <v>182908498</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>113288</v>
+        <v>69648</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>114760241</v>
+        <v>103516828</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>114700927</v>
+        <v>103483283</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>59314</v>
+        <v>33545</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2.81</v>
+        <v>3.12</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0672</v>
+        <v>0.0379</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>722170520</v>
+        <v>649152184</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>721768366</v>
+        <v>648903503</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>402154</v>
+        <v>248681</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2.74</v>
+        <v>3.03</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.0742</v>
+        <v>0.0462</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/주별투자수익_2026-08-03_2026-08-27.xlsx
+++ b/assets/xlsx/주별투자수익_2026-08-03_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>182300961</v>
+        <v>182419789</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>182219113</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>81830</v>
+        <v>200658</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>2.93</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.056</v>
+        <v>0.1372</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>180356275</v>
+        <v>180491152</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>180292609</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>63658</v>
+        <v>198535</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3.07</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.042</v>
+        <v>0.1309</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>182978149</v>
+        <v>183109919</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>182908498</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>69648</v>
+        <v>201418</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.04</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0458</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>103516848</v>
+        <v>103597259</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>103483283</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>33545</v>
+        <v>113956</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0379</v>
+        <v>0.1288</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>649152233</v>
+        <v>649618119</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>648903503</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>248681</v>
+        <v>714567</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>3.03</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.0462</v>
+        <v>0.1327</v>
       </c>
     </row>
   </sheetData>
